--- a/excel/Debitum Rima.xlsx
+++ b/excel/Debitum Rima.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Debitum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7AAAE19-5875-4264-AA6E-257177721AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12504A4-0BCB-4907-9EBF-53656F152535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -1393,7 +1393,7 @@
       <c r="P3" s="9"/>
       <c r="Q3" s="29">
         <f>Pinigai!I2</f>
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="R3" s="29">
         <f>SUM(H3:H100)-U3</f>
@@ -1401,11 +1401,11 @@
       </c>
       <c r="S3" s="30">
         <f>Pinigai!H2</f>
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="T3" s="30">
         <f>W3-R3</f>
-        <v>139.26</v>
+        <v>78.37</v>
       </c>
       <c r="U3" s="29">
         <f>SUM(M3:M100)</f>
@@ -1417,19 +1417,19 @@
       </c>
       <c r="W3" s="30">
         <f>Q3+S3+V3</f>
-        <v>260.89</v>
+        <v>200</v>
       </c>
       <c r="X3" s="30">
         <f>W3-Q3</f>
-        <v>0.88999999999998636</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="31">
         <f>(W3-Q3)/Q3</f>
-        <v>3.4230769230768707E-3</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="32">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>6.8520873785018919E-3</v>
+        <v>2.9802322387695314E-9</v>
       </c>
       <c r="AA3" s="30">
         <f>SUM(O3:O100)</f>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>45922</v>
+        <v>46241</v>
       </c>
       <c r="B2" s="3">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="F2" s="3">
         <f>SUM(B2:B35)</f>
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="G2" s="3">
         <f>SUM(C2:C35)</f>
@@ -2182,213 +2182,125 @@
       </c>
       <c r="H2" s="3">
         <f>SUM(D2:D35)</f>
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="I2" s="3">
         <f>F2-G2</f>
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="K2" s="3">
         <f t="shared" ref="K2:K13" si="0">B2*-1</f>
-        <v>-50</v>
+        <v>-200</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
-        <v>45972</v>
-      </c>
-      <c r="B3" s="3">
-        <v>50</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0</v>
-      </c>
+      <c r="A3" s="6"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
       <c r="K3" s="3">
         <f t="shared" si="0"/>
-        <v>-50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <v>46006</v>
-      </c>
-      <c r="B4" s="3">
-        <v>20</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0</v>
-      </c>
+      <c r="A4" s="6"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
       <c r="K4" s="3">
         <f t="shared" si="0"/>
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <v>46024</v>
-      </c>
-      <c r="B5" s="3">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0</v>
-      </c>
+      <c r="A5" s="6"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
       <c r="K5" s="3">
         <f t="shared" si="0"/>
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>46064</v>
-      </c>
-      <c r="B6" s="3">
-        <v>20</v>
-      </c>
-      <c r="C6" s="3">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3">
-        <v>0</v>
-      </c>
+      <c r="A6" s="6"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
       <c r="K6" s="3">
         <f t="shared" si="0"/>
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <v>46128</v>
-      </c>
-      <c r="B7" s="3">
-        <v>20</v>
-      </c>
-      <c r="C7" s="3">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3">
-        <v>0.34</v>
-      </c>
+      <c r="A7" s="6"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
       <c r="K7" s="3">
         <f t="shared" si="0"/>
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>46144</v>
-      </c>
-      <c r="B8" s="3">
-        <v>20</v>
-      </c>
-      <c r="C8" s="3">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3">
-        <v>0</v>
-      </c>
+      <c r="A8" s="6"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
       <c r="K8" s="3">
         <f t="shared" si="0"/>
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
-        <v>46147</v>
-      </c>
-      <c r="B9" s="3">
-        <v>0</v>
-      </c>
-      <c r="C9" s="3">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3">
-        <v>0.15</v>
-      </c>
+      <c r="A9" s="6"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
       <c r="K9" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <v>46169</v>
-      </c>
-      <c r="B10" s="3">
-        <v>0</v>
-      </c>
-      <c r="C10" s="3">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3">
-        <v>0.4</v>
-      </c>
+      <c r="A10" s="6"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
       <c r="K10" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
-        <v>46205</v>
-      </c>
-      <c r="B11" s="3">
-        <v>20</v>
-      </c>
-      <c r="C11" s="3">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3">
-        <v>0</v>
-      </c>
+      <c r="A11" s="6"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
       <c r="K11" s="3">
         <f t="shared" si="0"/>
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
-        <v>46217</v>
-      </c>
-      <c r="B12" s="3">
-        <v>20</v>
-      </c>
-      <c r="C12" s="3">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3">
-        <v>0</v>
-      </c>
+      <c r="A12" s="6"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
       <c r="K12" s="3">
         <f t="shared" si="0"/>
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
-        <v>46237</v>
-      </c>
-      <c r="B13" s="3">
-        <v>20</v>
-      </c>
-      <c r="C13" s="3">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3">
-        <v>0</v>
-      </c>
+      <c r="A13" s="6"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
       <c r="K13" s="3">
         <f t="shared" si="0"/>
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -3703,7 +3615,7 @@
       <c r="D200" s="1"/>
       <c r="K200" s="3">
         <f>Overview!W3</f>
-        <v>260.89</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/excel/Debitum Rima.xlsx
+++ b/excel/Debitum Rima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Debitum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812E7999-8696-44B7-BCB4-73A085B51A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C5FC94-3329-405A-B3D0-9390BEE8EC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="K3" s="20">
         <f ca="1">'LV0000112472'!B12</f>
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="L3" s="2" t="str">
         <f ca="1">'LV0000112472'!P3</f>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="N3" s="3">
         <f>'LV0000112472'!L3</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="O3" s="3">
         <f>'LV0000112472'!M3</f>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="T3" s="30">
         <f>W3-R3</f>
-        <v>0</v>
+        <v>1.3000000000000114</v>
       </c>
       <c r="U3" s="29">
         <f>SUM(M3:M100)</f>
@@ -1789,27 +1789,27 @@
       </c>
       <c r="V3" s="29">
         <f>SUM(N3:N100)-AA3</f>
-        <v>0</v>
+        <v>1.2999999999999998</v>
       </c>
       <c r="W3" s="30">
         <f>Q3+S3+V3</f>
-        <v>200</v>
+        <v>201.3</v>
       </c>
       <c r="X3" s="30">
         <f>W3-Q3</f>
-        <v>0</v>
+        <v>1.3000000000000114</v>
       </c>
       <c r="Y3" s="31">
         <f>(W3-Q3)/Q3</f>
-        <v>0</v>
+        <v>6.5000000000000569E-3</v>
       </c>
       <c r="Z3" s="32">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>2.9802322387695314E-9</v>
+        <v>9.9211281538009621E-2</v>
       </c>
       <c r="AA3" s="30">
         <f>SUM(O3:O100)</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AC3" s="3" t="str">
         <f ca="1">'LV0000112472'!Z3</f>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="K4" s="20">
         <f ca="1">'LV0000112910'!B12</f>
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="L4" s="2" t="str">
         <f ca="1">'LV0000112910'!P3</f>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="N4" s="3">
         <f>'LV0000112910'!L3</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="O4" s="3">
         <f>'LV0000112910'!M3</f>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="K5" s="20">
         <f ca="1">'LV0000112886'!B12</f>
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="L5" s="2" t="str">
         <f ca="1">'LV0000112886'!P3</f>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="N5" s="3">
         <f>'LV0000112886'!L3</f>
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="O5" s="3">
         <f>'LV0000112886'!M3</f>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="K6" s="20">
         <f ca="1">'LV0000112894'!B12</f>
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="L6" s="2" t="str">
         <f ca="1">'LV0000112894'!P3</f>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="N6" s="3">
         <f>'LV0000112894'!L3</f>
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="O6" s="3">
         <f>'LV0000112894'!M3</f>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K7" s="20">
         <f ca="1">'LV0000112688 '!B12</f>
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L7" s="2" t="str">
         <f ca="1">'LV0000112688 '!P3</f>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="N7" s="3">
         <f>'LV0000112688 '!L3</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="O7" s="3">
         <f>'LV0000112688 '!M3</f>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K8" s="20">
         <f ca="1">'LV0000112548'!B12</f>
-        <v>350</v>
+        <v>328</v>
       </c>
       <c r="L8" s="2" t="str">
         <f ca="1">'LV0000112548'!P3</f>
@@ -2144,11 +2144,11 @@
       </c>
       <c r="N8" s="3">
         <f>'LV0000112548'!L3</f>
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="O8" s="3">
         <f>'LV0000112548'!M3</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="P8" s="9"/>
       <c r="AC8" s="3" t="str">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="K9" s="20">
         <f ca="1">'LV0000112530'!B12</f>
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="L9" s="2" t="str">
         <f ca="1">'LV0000112530'!P3</f>
@@ -2210,11 +2210,11 @@
       </c>
       <c r="N9" s="3">
         <f>'LV0000112530'!L3</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O9" s="3">
         <f>'LV0000112530'!M3</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="P9" s="9"/>
       <c r="AC9" s="3" t="str">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="K10" s="20">
         <f ca="1">'LV0000112076'!B12</f>
-        <v>661</v>
+        <v>639</v>
       </c>
       <c r="L10" s="2" t="str">
         <f ca="1">'LV0000112076'!P3</f>
@@ -2276,11 +2276,11 @@
       </c>
       <c r="N10" s="3">
         <f>'LV0000112076'!L3</f>
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="O10" s="3">
         <f>'LV0000112076'!M3</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="P10" s="9"/>
       <c r="AC10" s="3" t="str">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="K11" s="20">
         <f ca="1">'LV0000112241'!B12</f>
-        <v>697</v>
+        <v>675</v>
       </c>
       <c r="L11" s="2" t="str">
         <f ca="1">'LV0000112241'!P3</f>
@@ -2342,11 +2342,11 @@
       </c>
       <c r="N11" s="3">
         <f>'LV0000112241'!L3</f>
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="O11" s="3">
         <f>'LV0000112241'!M3</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AC11" s="3" t="str">
         <f ca="1">'LV0000112241'!Z3</f>
@@ -2802,14 +2802,22 @@
       <c r="D3" s="13">
         <v>46265</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="20" t="str">
+      <c r="E3" s="13">
+        <v>46265</v>
+      </c>
+      <c r="F3" s="20">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
       <c r="J3" s="15"/>
       <c r="K3" s="3">
         <f>G53</f>
@@ -2817,7 +2825,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -2869,11 +2877,11 @@
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -3040,7 +3048,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -3107,7 +3115,7 @@
       <c r="D15" s="13"/>
       <c r="E15" s="6"/>
       <c r="F15" s="20" t="str">
-        <f t="shared" ref="F5:F52" si="2">IF(E15&gt;0,E15-D15,"")</f>
+        <f t="shared" ref="F15:F52" si="2">IF(E15&gt;0,E15-D15,"")</f>
         <v/>
       </c>
       <c r="G15" s="2"/>
@@ -3895,7 +3903,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -4050,14 +4058,22 @@
       <c r="D3" s="13">
         <v>46265</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="20" t="str">
+      <c r="E3" s="13">
+        <v>46265</v>
+      </c>
+      <c r="F3" s="20">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
       <c r="J3" s="15"/>
       <c r="K3" s="3">
         <f>G53</f>
@@ -4065,7 +4081,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -4117,11 +4133,11 @@
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -4288,7 +4304,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -4332,7 +4348,7 @@
       <c r="D14" s="13"/>
       <c r="E14" s="6"/>
       <c r="F14" s="20" t="str">
-        <f t="shared" ref="F5:F52" si="2">IF(E14&gt;0,E14-D14,"")</f>
+        <f t="shared" ref="F14:F52" si="2">IF(E14&gt;0,E14-D14,"")</f>
         <v/>
       </c>
       <c r="G14" s="2"/>
@@ -5146,7 +5162,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -6675,14 +6691,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46266</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="K200" s="3">
         <f>Overview!W3</f>
-        <v>200</v>
+        <v>201.3</v>
       </c>
     </row>
   </sheetData>
@@ -6809,14 +6825,22 @@
       <c r="D3" s="13">
         <v>46265</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="20" t="str">
+      <c r="E3" s="13">
+        <v>46265</v>
+      </c>
+      <c r="F3" s="20">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.01</v>
+      </c>
       <c r="J3" s="15"/>
       <c r="K3" s="3">
         <f>G53</f>
@@ -6824,11 +6848,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -6879,11 +6903,11 @@
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0</v>
+        <v>0.13999999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -7071,7 +7095,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>697</v>
+        <v>675</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -7935,11 +7959,11 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -8090,14 +8114,22 @@
       <c r="D3" s="13">
         <v>46265</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="20" t="str">
+      <c r="E3" s="13">
+        <v>46265</v>
+      </c>
+      <c r="F3" s="20">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.01</v>
+      </c>
       <c r="J3" s="15"/>
       <c r="K3" s="3">
         <f>G53</f>
@@ -8105,11 +8137,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -8160,11 +8192,11 @@
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0</v>
+        <v>0.13999999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -8352,7 +8384,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>661</v>
+        <v>639</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -9216,11 +9248,11 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -9371,14 +9403,22 @@
       <c r="D3" s="13">
         <v>46265</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="20" t="str">
+      <c r="E3" s="13">
+        <v>46265</v>
+      </c>
+      <c r="F3" s="20">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.01</v>
+      </c>
       <c r="J3" s="15"/>
       <c r="K3" s="3">
         <f>G53</f>
@@ -9386,11 +9426,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -9441,11 +9481,11 @@
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -9633,7 +9673,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -10497,11 +10537,11 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -10652,14 +10692,22 @@
       <c r="D3" s="13">
         <v>46265</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="20" t="str">
+      <c r="E3" s="13">
+        <v>46265</v>
+      </c>
+      <c r="F3" s="20">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.01</v>
+      </c>
       <c r="J3" s="15"/>
       <c r="K3" s="3">
         <f>G53</f>
@@ -10667,11 +10715,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -10722,11 +10770,11 @@
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0</v>
+        <v>0.19999999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -10914,7 +10962,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>350</v>
+        <v>328</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -11778,11 +11826,11 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -11934,14 +11982,22 @@
       <c r="D3" s="13">
         <v>46265</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="20" t="str">
+      <c r="E3" s="13">
+        <v>46265</v>
+      </c>
+      <c r="F3" s="20">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
       <c r="J3" s="15"/>
       <c r="K3" s="3">
         <f>G53</f>
@@ -11949,7 +12005,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -12004,11 +12060,11 @@
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -12196,7 +12252,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -13060,7 +13116,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -13215,14 +13271,22 @@
       <c r="D3" s="13">
         <v>46265</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="20" t="str">
+      <c r="E3" s="13">
+        <v>46265</v>
+      </c>
+      <c r="F3" s="20">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
       <c r="J3" s="15"/>
       <c r="K3" s="3">
         <f>G53</f>
@@ -13230,7 +13294,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -13285,11 +13349,11 @@
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -13477,7 +13541,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -14341,7 +14405,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -14496,14 +14560,22 @@
       <c r="D3" s="13">
         <v>46265</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="20" t="str">
+      <c r="E3" s="13">
+        <v>46265</v>
+      </c>
+      <c r="F3" s="20">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
       <c r="J3" s="15"/>
       <c r="K3" s="3">
         <f>G53</f>
@@ -14511,7 +14583,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -14566,11 +14638,11 @@
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -14758,7 +14830,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -15622,7 +15694,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
